--- a/analytikI/priklad.xlsx
+++ b/analytikI/priklad.xlsx
@@ -124,6 +124,145 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Tržby podľa produktu</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Predaj'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Predaj'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Predaj'!$D$2:$D$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Produkt</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>€</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -488,5 +627,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/analytikI/priklad.xlsx
+++ b/analytikI/priklad.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predaj" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tablib Dataset" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,145 +126,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Tržby podľa produktu</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Predaj'!D1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Predaj'!$A$2:$A$4</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Predaj'!$D$2:$D$4</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Produkt</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>€</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>14</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -552,81 +417,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="3" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Produkt</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Cena</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Kusov</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Spolu (€)</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>meno</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>vek</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>city</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chleba</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D2" t="n">
-        <v>15</v>
+          <t>Janko</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mlieko</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="n">
-        <v>18</v>
+          <t>Katka</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Košice</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maslo</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>11.5</v>
+          <t>Robo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lenka</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prešov</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Miro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Banska, Bystrica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Janko</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Katka</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>22</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Košice</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Robo</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vlado</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>36</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Robo</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Robo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>38</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Zvolen</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>